--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_96mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_96mo.xlsx
@@ -1367,20 +1367,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>96</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -1479,15 +1514,15 @@
       <c r="DD2" s="21" t="n"/>
       <c r="DE2" s="21" t="n"/>
       <c r="DF2" s="24">
-        <f>SUM(M2:DD2)</f>
+        <f>H2+SUM(M2:DD2)</f>
         <v/>
       </c>
       <c r="DG2" s="24">
-        <f>I2-DF2</f>
+        <f>I2-H2-SUM(M2:DD2)</f>
         <v/>
       </c>
       <c r="DH2" s="25">
-        <f>IF(I2=0,"",DF2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:DD2))/I2)</f>
         <v/>
       </c>
       <c r="DI2" s="26" t="n"/>
@@ -1612,15 +1647,15 @@
       <c r="DD3" s="21" t="n"/>
       <c r="DE3" s="21" t="n"/>
       <c r="DF3" s="24">
-        <f>SUM(M3:DD3)</f>
+        <f>H3+SUM(M3:DD3)</f>
         <v/>
       </c>
       <c r="DG3" s="24">
-        <f>I3-DF3</f>
+        <f>I3-H3-SUM(M3:DD3)</f>
         <v/>
       </c>
       <c r="DH3" s="25">
-        <f>IF(I3=0,"",DF3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:DD3))/I3)</f>
         <v/>
       </c>
       <c r="DI3" s="26" t="n"/>
@@ -1745,15 +1780,15 @@
       <c r="DD4" s="21" t="n"/>
       <c r="DE4" s="21" t="n"/>
       <c r="DF4" s="24">
-        <f>SUM(M4:DD4)</f>
+        <f>H4+SUM(M4:DD4)</f>
         <v/>
       </c>
       <c r="DG4" s="24">
-        <f>I4-DF4</f>
+        <f>I4-H4-SUM(M4:DD4)</f>
         <v/>
       </c>
       <c r="DH4" s="25">
-        <f>IF(I4=0,"",DF4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:DD4))/I4)</f>
         <v/>
       </c>
       <c r="DI4" s="26" t="n"/>
@@ -1878,15 +1913,15 @@
       <c r="DD5" s="21" t="n"/>
       <c r="DE5" s="21" t="n"/>
       <c r="DF5" s="24">
-        <f>SUM(M5:DD5)</f>
+        <f>H5+SUM(M5:DD5)</f>
         <v/>
       </c>
       <c r="DG5" s="24">
-        <f>I5-DF5</f>
+        <f>I5-H5-SUM(M5:DD5)</f>
         <v/>
       </c>
       <c r="DH5" s="25">
-        <f>IF(I5=0,"",DF5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:DD5))/I5)</f>
         <v/>
       </c>
       <c r="DI5" s="26" t="n"/>
@@ -2011,15 +2046,15 @@
       <c r="DD6" s="21" t="n"/>
       <c r="DE6" s="21" t="n"/>
       <c r="DF6" s="24">
-        <f>SUM(M6:DD6)</f>
+        <f>H6+SUM(M6:DD6)</f>
         <v/>
       </c>
       <c r="DG6" s="24">
-        <f>I6-DF6</f>
+        <f>I6-H6-SUM(M6:DD6)</f>
         <v/>
       </c>
       <c r="DH6" s="25">
-        <f>IF(I6=0,"",DF6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:DD6))/I6)</f>
         <v/>
       </c>
       <c r="DI6" s="26" t="n"/>
@@ -2144,15 +2179,15 @@
       <c r="DD7" s="21" t="n"/>
       <c r="DE7" s="21" t="n"/>
       <c r="DF7" s="24">
-        <f>SUM(M7:DD7)</f>
+        <f>H7+SUM(M7:DD7)</f>
         <v/>
       </c>
       <c r="DG7" s="24">
-        <f>I7-DF7</f>
+        <f>I7-H7-SUM(M7:DD7)</f>
         <v/>
       </c>
       <c r="DH7" s="25">
-        <f>IF(I7=0,"",DF7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:DD7))/I7)</f>
         <v/>
       </c>
       <c r="DI7" s="26" t="n"/>
@@ -2277,15 +2312,15 @@
       <c r="DD8" s="21" t="n"/>
       <c r="DE8" s="21" t="n"/>
       <c r="DF8" s="24">
-        <f>SUM(M8:DD8)</f>
+        <f>H8+SUM(M8:DD8)</f>
         <v/>
       </c>
       <c r="DG8" s="24">
-        <f>I8-DF8</f>
+        <f>I8-H8-SUM(M8:DD8)</f>
         <v/>
       </c>
       <c r="DH8" s="25">
-        <f>IF(I8=0,"",DF8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:DD8))/I8)</f>
         <v/>
       </c>
       <c r="DI8" s="26" t="n"/>
@@ -2410,15 +2445,15 @@
       <c r="DD9" s="21" t="n"/>
       <c r="DE9" s="21" t="n"/>
       <c r="DF9" s="24">
-        <f>SUM(M9:DD9)</f>
+        <f>H9+SUM(M9:DD9)</f>
         <v/>
       </c>
       <c r="DG9" s="24">
-        <f>I9-DF9</f>
+        <f>I9-H9-SUM(M9:DD9)</f>
         <v/>
       </c>
       <c r="DH9" s="25">
-        <f>IF(I9=0,"",DF9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:DD9))/I9)</f>
         <v/>
       </c>
       <c r="DI9" s="26" t="n"/>
@@ -2543,15 +2578,15 @@
       <c r="DD10" s="21" t="n"/>
       <c r="DE10" s="21" t="n"/>
       <c r="DF10" s="24">
-        <f>SUM(M10:DD10)</f>
+        <f>H10+SUM(M10:DD10)</f>
         <v/>
       </c>
       <c r="DG10" s="24">
-        <f>I10-DF10</f>
+        <f>I10-H10-SUM(M10:DD10)</f>
         <v/>
       </c>
       <c r="DH10" s="25">
-        <f>IF(I10=0,"",DF10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:DD10))/I10)</f>
         <v/>
       </c>
       <c r="DI10" s="26" t="n"/>
@@ -2676,15 +2711,15 @@
       <c r="DD11" s="21" t="n"/>
       <c r="DE11" s="21" t="n"/>
       <c r="DF11" s="24">
-        <f>SUM(M11:DD11)</f>
+        <f>H11+SUM(M11:DD11)</f>
         <v/>
       </c>
       <c r="DG11" s="24">
-        <f>I11-DF11</f>
+        <f>I11-H11-SUM(M11:DD11)</f>
         <v/>
       </c>
       <c r="DH11" s="25">
-        <f>IF(I11=0,"",DF11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:DD11))/I11)</f>
         <v/>
       </c>
       <c r="DI11" s="26" t="n"/>
@@ -2809,15 +2844,15 @@
       <c r="DD12" s="21" t="n"/>
       <c r="DE12" s="21" t="n"/>
       <c r="DF12" s="24">
-        <f>SUM(M12:DD12)</f>
+        <f>H12+SUM(M12:DD12)</f>
         <v/>
       </c>
       <c r="DG12" s="24">
-        <f>I12-DF12</f>
+        <f>I12-H12-SUM(M12:DD12)</f>
         <v/>
       </c>
       <c r="DH12" s="25">
-        <f>IF(I12=0,"",DF12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:DD12))/I12)</f>
         <v/>
       </c>
       <c r="DI12" s="26" t="n"/>
@@ -2942,15 +2977,15 @@
       <c r="DD13" s="21" t="n"/>
       <c r="DE13" s="21" t="n"/>
       <c r="DF13" s="24">
-        <f>SUM(M13:DD13)</f>
+        <f>H13+SUM(M13:DD13)</f>
         <v/>
       </c>
       <c r="DG13" s="24">
-        <f>I13-DF13</f>
+        <f>I13-H13-SUM(M13:DD13)</f>
         <v/>
       </c>
       <c r="DH13" s="25">
-        <f>IF(I13=0,"",DF13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:DD13))/I13)</f>
         <v/>
       </c>
       <c r="DI13" s="26" t="n"/>
@@ -3075,15 +3110,15 @@
       <c r="DD14" s="21" t="n"/>
       <c r="DE14" s="21" t="n"/>
       <c r="DF14" s="24">
-        <f>SUM(M14:DD14)</f>
+        <f>H14+SUM(M14:DD14)</f>
         <v/>
       </c>
       <c r="DG14" s="24">
-        <f>I14-DF14</f>
+        <f>I14-H14-SUM(M14:DD14)</f>
         <v/>
       </c>
       <c r="DH14" s="25">
-        <f>IF(I14=0,"",DF14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:DD14))/I14)</f>
         <v/>
       </c>
       <c r="DI14" s="26" t="n"/>
@@ -3208,15 +3243,15 @@
       <c r="DD15" s="21" t="n"/>
       <c r="DE15" s="21" t="n"/>
       <c r="DF15" s="24">
-        <f>SUM(M15:DD15)</f>
+        <f>H15+SUM(M15:DD15)</f>
         <v/>
       </c>
       <c r="DG15" s="24">
-        <f>I15-DF15</f>
+        <f>I15-H15-SUM(M15:DD15)</f>
         <v/>
       </c>
       <c r="DH15" s="25">
-        <f>IF(I15=0,"",DF15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:DD15))/I15)</f>
         <v/>
       </c>
       <c r="DI15" s="26" t="n"/>
@@ -3341,15 +3376,15 @@
       <c r="DD16" s="21" t="n"/>
       <c r="DE16" s="21" t="n"/>
       <c r="DF16" s="24">
-        <f>SUM(M16:DD16)</f>
+        <f>H16+SUM(M16:DD16)</f>
         <v/>
       </c>
       <c r="DG16" s="24">
-        <f>I16-DF16</f>
+        <f>I16-H16-SUM(M16:DD16)</f>
         <v/>
       </c>
       <c r="DH16" s="25">
-        <f>IF(I16=0,"",DF16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:DD16))/I16)</f>
         <v/>
       </c>
       <c r="DI16" s="26" t="n"/>
@@ -3474,15 +3509,15 @@
       <c r="DD17" s="21" t="n"/>
       <c r="DE17" s="21" t="n"/>
       <c r="DF17" s="24">
-        <f>SUM(M17:DD17)</f>
+        <f>H17+SUM(M17:DD17)</f>
         <v/>
       </c>
       <c r="DG17" s="24">
-        <f>I17-DF17</f>
+        <f>I17-H17-SUM(M17:DD17)</f>
         <v/>
       </c>
       <c r="DH17" s="25">
-        <f>IF(I17=0,"",DF17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:DD17))/I17)</f>
         <v/>
       </c>
       <c r="DI17" s="26" t="n"/>
@@ -3607,15 +3642,15 @@
       <c r="DD18" s="21" t="n"/>
       <c r="DE18" s="21" t="n"/>
       <c r="DF18" s="24">
-        <f>SUM(M18:DD18)</f>
+        <f>H18+SUM(M18:DD18)</f>
         <v/>
       </c>
       <c r="DG18" s="24">
-        <f>I18-DF18</f>
+        <f>I18-H18-SUM(M18:DD18)</f>
         <v/>
       </c>
       <c r="DH18" s="25">
-        <f>IF(I18=0,"",DF18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:DD18))/I18)</f>
         <v/>
       </c>
       <c r="DI18" s="26" t="n"/>
@@ -3740,15 +3775,15 @@
       <c r="DD19" s="21" t="n"/>
       <c r="DE19" s="21" t="n"/>
       <c r="DF19" s="24">
-        <f>SUM(M19:DD19)</f>
+        <f>H19+SUM(M19:DD19)</f>
         <v/>
       </c>
       <c r="DG19" s="24">
-        <f>I19-DF19</f>
+        <f>I19-H19-SUM(M19:DD19)</f>
         <v/>
       </c>
       <c r="DH19" s="25">
-        <f>IF(I19=0,"",DF19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:DD19))/I19)</f>
         <v/>
       </c>
       <c r="DI19" s="26" t="n"/>
@@ -3873,15 +3908,15 @@
       <c r="DD20" s="21" t="n"/>
       <c r="DE20" s="21" t="n"/>
       <c r="DF20" s="24">
-        <f>SUM(M20:DD20)</f>
+        <f>H20+SUM(M20:DD20)</f>
         <v/>
       </c>
       <c r="DG20" s="24">
-        <f>I20-DF20</f>
+        <f>I20-H20-SUM(M20:DD20)</f>
         <v/>
       </c>
       <c r="DH20" s="25">
-        <f>IF(I20=0,"",DF20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:DD20))/I20)</f>
         <v/>
       </c>
       <c r="DI20" s="26" t="n"/>
@@ -4006,15 +4041,15 @@
       <c r="DD21" s="21" t="n"/>
       <c r="DE21" s="21" t="n"/>
       <c r="DF21" s="24">
-        <f>SUM(M21:DD21)</f>
+        <f>H21+SUM(M21:DD21)</f>
         <v/>
       </c>
       <c r="DG21" s="24">
-        <f>I21-DF21</f>
+        <f>I21-H21-SUM(M21:DD21)</f>
         <v/>
       </c>
       <c r="DH21" s="25">
-        <f>IF(I21=0,"",DF21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:DD21))/I21)</f>
         <v/>
       </c>
       <c r="DI21" s="26" t="n"/>
@@ -4139,15 +4174,15 @@
       <c r="DD22" s="21" t="n"/>
       <c r="DE22" s="21" t="n"/>
       <c r="DF22" s="24">
-        <f>SUM(M22:DD22)</f>
+        <f>H22+SUM(M22:DD22)</f>
         <v/>
       </c>
       <c r="DG22" s="24">
-        <f>I22-DF22</f>
+        <f>I22-H22-SUM(M22:DD22)</f>
         <v/>
       </c>
       <c r="DH22" s="25">
-        <f>IF(I22=0,"",DF22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:DD22))/I22)</f>
         <v/>
       </c>
       <c r="DI22" s="26" t="n"/>
@@ -4272,15 +4307,15 @@
       <c r="DD23" s="21" t="n"/>
       <c r="DE23" s="21" t="n"/>
       <c r="DF23" s="24">
-        <f>SUM(M23:DD23)</f>
+        <f>H23+SUM(M23:DD23)</f>
         <v/>
       </c>
       <c r="DG23" s="24">
-        <f>I23-DF23</f>
+        <f>I23-H23-SUM(M23:DD23)</f>
         <v/>
       </c>
       <c r="DH23" s="25">
-        <f>IF(I23=0,"",DF23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:DD23))/I23)</f>
         <v/>
       </c>
       <c r="DI23" s="26" t="n"/>
@@ -4405,15 +4440,15 @@
       <c r="DD24" s="21" t="n"/>
       <c r="DE24" s="21" t="n"/>
       <c r="DF24" s="24">
-        <f>SUM(M24:DD24)</f>
+        <f>H24+SUM(M24:DD24)</f>
         <v/>
       </c>
       <c r="DG24" s="24">
-        <f>I24-DF24</f>
+        <f>I24-H24-SUM(M24:DD24)</f>
         <v/>
       </c>
       <c r="DH24" s="25">
-        <f>IF(I24=0,"",DF24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:DD24))/I24)</f>
         <v/>
       </c>
       <c r="DI24" s="26" t="n"/>
@@ -4538,15 +4573,15 @@
       <c r="DD25" s="21" t="n"/>
       <c r="DE25" s="21" t="n"/>
       <c r="DF25" s="24">
-        <f>SUM(M25:DD25)</f>
+        <f>H25+SUM(M25:DD25)</f>
         <v/>
       </c>
       <c r="DG25" s="24">
-        <f>I25-DF25</f>
+        <f>I25-H25-SUM(M25:DD25)</f>
         <v/>
       </c>
       <c r="DH25" s="25">
-        <f>IF(I25=0,"",DF25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:DD25))/I25)</f>
         <v/>
       </c>
       <c r="DI25" s="26" t="n"/>
@@ -4671,15 +4706,15 @@
       <c r="DD26" s="21" t="n"/>
       <c r="DE26" s="21" t="n"/>
       <c r="DF26" s="24">
-        <f>SUM(M26:DD26)</f>
+        <f>H26+SUM(M26:DD26)</f>
         <v/>
       </c>
       <c r="DG26" s="24">
-        <f>I26-DF26</f>
+        <f>I26-H26-SUM(M26:DD26)</f>
         <v/>
       </c>
       <c r="DH26" s="25">
-        <f>IF(I26=0,"",DF26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:DD26))/I26)</f>
         <v/>
       </c>
       <c r="DI26" s="26" t="n"/>
@@ -4804,15 +4839,15 @@
       <c r="DD27" s="21" t="n"/>
       <c r="DE27" s="21" t="n"/>
       <c r="DF27" s="24">
-        <f>SUM(M27:DD27)</f>
+        <f>H27+SUM(M27:DD27)</f>
         <v/>
       </c>
       <c r="DG27" s="24">
-        <f>I27-DF27</f>
+        <f>I27-H27-SUM(M27:DD27)</f>
         <v/>
       </c>
       <c r="DH27" s="25">
-        <f>IF(I27=0,"",DF27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:DD27))/I27)</f>
         <v/>
       </c>
       <c r="DI27" s="26" t="n"/>
@@ -4937,15 +4972,15 @@
       <c r="DD28" s="21" t="n"/>
       <c r="DE28" s="21" t="n"/>
       <c r="DF28" s="24">
-        <f>SUM(M28:DD28)</f>
+        <f>H28+SUM(M28:DD28)</f>
         <v/>
       </c>
       <c r="DG28" s="24">
-        <f>I28-DF28</f>
+        <f>I28-H28-SUM(M28:DD28)</f>
         <v/>
       </c>
       <c r="DH28" s="25">
-        <f>IF(I28=0,"",DF28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:DD28))/I28)</f>
         <v/>
       </c>
       <c r="DI28" s="26" t="n"/>
@@ -5070,15 +5105,15 @@
       <c r="DD29" s="21" t="n"/>
       <c r="DE29" s="21" t="n"/>
       <c r="DF29" s="24">
-        <f>SUM(M29:DD29)</f>
+        <f>H29+SUM(M29:DD29)</f>
         <v/>
       </c>
       <c r="DG29" s="24">
-        <f>I29-DF29</f>
+        <f>I29-H29-SUM(M29:DD29)</f>
         <v/>
       </c>
       <c r="DH29" s="25">
-        <f>IF(I29=0,"",DF29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:DD29))/I29)</f>
         <v/>
       </c>
       <c r="DI29" s="26" t="n"/>
@@ -5203,15 +5238,15 @@
       <c r="DD30" s="21" t="n"/>
       <c r="DE30" s="21" t="n"/>
       <c r="DF30" s="24">
-        <f>SUM(M30:DD30)</f>
+        <f>H30+SUM(M30:DD30)</f>
         <v/>
       </c>
       <c r="DG30" s="24">
-        <f>I30-DF30</f>
+        <f>I30-H30-SUM(M30:DD30)</f>
         <v/>
       </c>
       <c r="DH30" s="25">
-        <f>IF(I30=0,"",DF30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:DD30))/I30)</f>
         <v/>
       </c>
       <c r="DI30" s="26" t="n"/>
@@ -5336,15 +5371,15 @@
       <c r="DD31" s="21" t="n"/>
       <c r="DE31" s="21" t="n"/>
       <c r="DF31" s="24">
-        <f>SUM(M31:DD31)</f>
+        <f>H31+SUM(M31:DD31)</f>
         <v/>
       </c>
       <c r="DG31" s="24">
-        <f>I31-DF31</f>
+        <f>I31-H31-SUM(M31:DD31)</f>
         <v/>
       </c>
       <c r="DH31" s="25">
-        <f>IF(I31=0,"",DF31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:DD31))/I31)</f>
         <v/>
       </c>
       <c r="DI31" s="26" t="n"/>
@@ -5469,15 +5504,15 @@
       <c r="DD32" s="21" t="n"/>
       <c r="DE32" s="21" t="n"/>
       <c r="DF32" s="24">
-        <f>SUM(M32:DD32)</f>
+        <f>H32+SUM(M32:DD32)</f>
         <v/>
       </c>
       <c r="DG32" s="24">
-        <f>I32-DF32</f>
+        <f>I32-H32-SUM(M32:DD32)</f>
         <v/>
       </c>
       <c r="DH32" s="25">
-        <f>IF(I32=0,"",DF32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:DD32))/I32)</f>
         <v/>
       </c>
       <c r="DI32" s="26" t="n"/>
@@ -5602,15 +5637,15 @@
       <c r="DD33" s="21" t="n"/>
       <c r="DE33" s="21" t="n"/>
       <c r="DF33" s="24">
-        <f>SUM(M33:DD33)</f>
+        <f>H33+SUM(M33:DD33)</f>
         <v/>
       </c>
       <c r="DG33" s="24">
-        <f>I33-DF33</f>
+        <f>I33-H33-SUM(M33:DD33)</f>
         <v/>
       </c>
       <c r="DH33" s="25">
-        <f>IF(I33=0,"",DF33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:DD33))/I33)</f>
         <v/>
       </c>
       <c r="DI33" s="26" t="n"/>
@@ -5735,15 +5770,15 @@
       <c r="DD34" s="21" t="n"/>
       <c r="DE34" s="21" t="n"/>
       <c r="DF34" s="24">
-        <f>SUM(M34:DD34)</f>
+        <f>H34+SUM(M34:DD34)</f>
         <v/>
       </c>
       <c r="DG34" s="24">
-        <f>I34-DF34</f>
+        <f>I34-H34-SUM(M34:DD34)</f>
         <v/>
       </c>
       <c r="DH34" s="25">
-        <f>IF(I34=0,"",DF34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:DD34))/I34)</f>
         <v/>
       </c>
       <c r="DI34" s="26" t="n"/>
@@ -5868,15 +5903,15 @@
       <c r="DD35" s="21" t="n"/>
       <c r="DE35" s="21" t="n"/>
       <c r="DF35" s="24">
-        <f>SUM(M35:DD35)</f>
+        <f>H35+SUM(M35:DD35)</f>
         <v/>
       </c>
       <c r="DG35" s="24">
-        <f>I35-DF35</f>
+        <f>I35-H35-SUM(M35:DD35)</f>
         <v/>
       </c>
       <c r="DH35" s="25">
-        <f>IF(I35=0,"",DF35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:DD35))/I35)</f>
         <v/>
       </c>
       <c r="DI35" s="26" t="n"/>
@@ -6001,15 +6036,15 @@
       <c r="DD36" s="21" t="n"/>
       <c r="DE36" s="21" t="n"/>
       <c r="DF36" s="24">
-        <f>SUM(M36:DD36)</f>
+        <f>H36+SUM(M36:DD36)</f>
         <v/>
       </c>
       <c r="DG36" s="24">
-        <f>I36-DF36</f>
+        <f>I36-H36-SUM(M36:DD36)</f>
         <v/>
       </c>
       <c r="DH36" s="25">
-        <f>IF(I36=0,"",DF36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:DD36))/I36)</f>
         <v/>
       </c>
       <c r="DI36" s="26" t="n"/>
@@ -6134,15 +6169,15 @@
       <c r="DD37" s="21" t="n"/>
       <c r="DE37" s="21" t="n"/>
       <c r="DF37" s="24">
-        <f>SUM(M37:DD37)</f>
+        <f>H37+SUM(M37:DD37)</f>
         <v/>
       </c>
       <c r="DG37" s="24">
-        <f>I37-DF37</f>
+        <f>I37-H37-SUM(M37:DD37)</f>
         <v/>
       </c>
       <c r="DH37" s="25">
-        <f>IF(I37=0,"",DF37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:DD37))/I37)</f>
         <v/>
       </c>
       <c r="DI37" s="26" t="n"/>
@@ -6267,15 +6302,15 @@
       <c r="DD38" s="21" t="n"/>
       <c r="DE38" s="21" t="n"/>
       <c r="DF38" s="24">
-        <f>SUM(M38:DD38)</f>
+        <f>H38+SUM(M38:DD38)</f>
         <v/>
       </c>
       <c r="DG38" s="24">
-        <f>I38-DF38</f>
+        <f>I38-H38-SUM(M38:DD38)</f>
         <v/>
       </c>
       <c r="DH38" s="25">
-        <f>IF(I38=0,"",DF38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:DD38))/I38)</f>
         <v/>
       </c>
       <c r="DI38" s="26" t="n"/>
@@ -6400,15 +6435,15 @@
       <c r="DD39" s="21" t="n"/>
       <c r="DE39" s="21" t="n"/>
       <c r="DF39" s="24">
-        <f>SUM(M39:DD39)</f>
+        <f>H39+SUM(M39:DD39)</f>
         <v/>
       </c>
       <c r="DG39" s="24">
-        <f>I39-DF39</f>
+        <f>I39-H39-SUM(M39:DD39)</f>
         <v/>
       </c>
       <c r="DH39" s="25">
-        <f>IF(I39=0,"",DF39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:DD39))/I39)</f>
         <v/>
       </c>
       <c r="DI39" s="26" t="n"/>
@@ -6533,15 +6568,15 @@
       <c r="DD40" s="21" t="n"/>
       <c r="DE40" s="21" t="n"/>
       <c r="DF40" s="24">
-        <f>SUM(M40:DD40)</f>
+        <f>H40+SUM(M40:DD40)</f>
         <v/>
       </c>
       <c r="DG40" s="24">
-        <f>I40-DF40</f>
+        <f>I40-H40-SUM(M40:DD40)</f>
         <v/>
       </c>
       <c r="DH40" s="25">
-        <f>IF(I40=0,"",DF40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:DD40))/I40)</f>
         <v/>
       </c>
       <c r="DI40" s="26" t="n"/>
@@ -6666,15 +6701,15 @@
       <c r="DD41" s="21" t="n"/>
       <c r="DE41" s="21" t="n"/>
       <c r="DF41" s="24">
-        <f>SUM(M41:DD41)</f>
+        <f>H41+SUM(M41:DD41)</f>
         <v/>
       </c>
       <c r="DG41" s="24">
-        <f>I41-DF41</f>
+        <f>I41-H41-SUM(M41:DD41)</f>
         <v/>
       </c>
       <c r="DH41" s="25">
-        <f>IF(I41=0,"",DF41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:DD41))/I41)</f>
         <v/>
       </c>
       <c r="DI41" s="26" t="n"/>
@@ -6799,15 +6834,15 @@
       <c r="DD42" s="21" t="n"/>
       <c r="DE42" s="21" t="n"/>
       <c r="DF42" s="24">
-        <f>SUM(M42:DD42)</f>
+        <f>H42+SUM(M42:DD42)</f>
         <v/>
       </c>
       <c r="DG42" s="24">
-        <f>I42-DF42</f>
+        <f>I42-H42-SUM(M42:DD42)</f>
         <v/>
       </c>
       <c r="DH42" s="25">
-        <f>IF(I42=0,"",DF42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:DD42))/I42)</f>
         <v/>
       </c>
       <c r="DI42" s="26" t="n"/>
@@ -6932,15 +6967,15 @@
       <c r="DD43" s="21" t="n"/>
       <c r="DE43" s="21" t="n"/>
       <c r="DF43" s="24">
-        <f>SUM(M43:DD43)</f>
+        <f>H43+SUM(M43:DD43)</f>
         <v/>
       </c>
       <c r="DG43" s="24">
-        <f>I43-DF43</f>
+        <f>I43-H43-SUM(M43:DD43)</f>
         <v/>
       </c>
       <c r="DH43" s="25">
-        <f>IF(I43=0,"",DF43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:DD43))/I43)</f>
         <v/>
       </c>
       <c r="DI43" s="26" t="n"/>
@@ -7065,15 +7100,15 @@
       <c r="DD44" s="21" t="n"/>
       <c r="DE44" s="21" t="n"/>
       <c r="DF44" s="24">
-        <f>SUM(M44:DD44)</f>
+        <f>H44+SUM(M44:DD44)</f>
         <v/>
       </c>
       <c r="DG44" s="24">
-        <f>I44-DF44</f>
+        <f>I44-H44-SUM(M44:DD44)</f>
         <v/>
       </c>
       <c r="DH44" s="25">
-        <f>IF(I44=0,"",DF44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:DD44))/I44)</f>
         <v/>
       </c>
       <c r="DI44" s="26" t="n"/>
@@ -7198,15 +7233,15 @@
       <c r="DD45" s="21" t="n"/>
       <c r="DE45" s="21" t="n"/>
       <c r="DF45" s="24">
-        <f>SUM(M45:DD45)</f>
+        <f>H45+SUM(M45:DD45)</f>
         <v/>
       </c>
       <c r="DG45" s="24">
-        <f>I45-DF45</f>
+        <f>I45-H45-SUM(M45:DD45)</f>
         <v/>
       </c>
       <c r="DH45" s="25">
-        <f>IF(I45=0,"",DF45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:DD45))/I45)</f>
         <v/>
       </c>
       <c r="DI45" s="26" t="n"/>
@@ -7331,15 +7366,15 @@
       <c r="DD46" s="21" t="n"/>
       <c r="DE46" s="21" t="n"/>
       <c r="DF46" s="24">
-        <f>SUM(M46:DD46)</f>
+        <f>H46+SUM(M46:DD46)</f>
         <v/>
       </c>
       <c r="DG46" s="24">
-        <f>I46-DF46</f>
+        <f>I46-H46-SUM(M46:DD46)</f>
         <v/>
       </c>
       <c r="DH46" s="25">
-        <f>IF(I46=0,"",DF46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:DD46))/I46)</f>
         <v/>
       </c>
       <c r="DI46" s="26" t="n"/>
@@ -7464,15 +7499,15 @@
       <c r="DD47" s="21" t="n"/>
       <c r="DE47" s="21" t="n"/>
       <c r="DF47" s="24">
-        <f>SUM(M47:DD47)</f>
+        <f>H47+SUM(M47:DD47)</f>
         <v/>
       </c>
       <c r="DG47" s="24">
-        <f>I47-DF47</f>
+        <f>I47-H47-SUM(M47:DD47)</f>
         <v/>
       </c>
       <c r="DH47" s="25">
-        <f>IF(I47=0,"",DF47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:DD47))/I47)</f>
         <v/>
       </c>
       <c r="DI47" s="26" t="n"/>
@@ -7597,15 +7632,15 @@
       <c r="DD48" s="21" t="n"/>
       <c r="DE48" s="21" t="n"/>
       <c r="DF48" s="24">
-        <f>SUM(M48:DD48)</f>
+        <f>H48+SUM(M48:DD48)</f>
         <v/>
       </c>
       <c r="DG48" s="24">
-        <f>I48-DF48</f>
+        <f>I48-H48-SUM(M48:DD48)</f>
         <v/>
       </c>
       <c r="DH48" s="25">
-        <f>IF(I48=0,"",DF48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:DD48))/I48)</f>
         <v/>
       </c>
       <c r="DI48" s="26" t="n"/>
@@ -7730,15 +7765,15 @@
       <c r="DD49" s="21" t="n"/>
       <c r="DE49" s="21" t="n"/>
       <c r="DF49" s="24">
-        <f>SUM(M49:DD49)</f>
+        <f>H49+SUM(M49:DD49)</f>
         <v/>
       </c>
       <c r="DG49" s="24">
-        <f>I49-DF49</f>
+        <f>I49-H49-SUM(M49:DD49)</f>
         <v/>
       </c>
       <c r="DH49" s="25">
-        <f>IF(I49=0,"",DF49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:DD49))/I49)</f>
         <v/>
       </c>
       <c r="DI49" s="26" t="n"/>
@@ -7863,15 +7898,15 @@
       <c r="DD50" s="21" t="n"/>
       <c r="DE50" s="21" t="n"/>
       <c r="DF50" s="24">
-        <f>SUM(M50:DD50)</f>
+        <f>H50+SUM(M50:DD50)</f>
         <v/>
       </c>
       <c r="DG50" s="24">
-        <f>I50-DF50</f>
+        <f>I50-H50-SUM(M50:DD50)</f>
         <v/>
       </c>
       <c r="DH50" s="25">
-        <f>IF(I50=0,"",DF50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:DD50))/I50)</f>
         <v/>
       </c>
       <c r="DI50" s="26" t="n"/>
@@ -7996,15 +8031,15 @@
       <c r="DD51" s="21" t="n"/>
       <c r="DE51" s="21" t="n"/>
       <c r="DF51" s="24">
-        <f>SUM(M51:DD51)</f>
+        <f>H51+SUM(M51:DD51)</f>
         <v/>
       </c>
       <c r="DG51" s="24">
-        <f>I51-DF51</f>
+        <f>I51-H51-SUM(M51:DD51)</f>
         <v/>
       </c>
       <c r="DH51" s="25">
-        <f>IF(I51=0,"",DF51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:DD51))/I51)</f>
         <v/>
       </c>
       <c r="DI51" s="26" t="n"/>
